--- a/ICGoNoGoDashboard_Working.xlsx
+++ b/ICGoNoGoDashboard_Working.xlsx
@@ -15,9 +15,9 @@
     <sheet name="Market Data" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="DealNames">Deals!$B$1:$L$1</definedName>
     <definedName name="MarketCounties">'Market Data'!$A$2:$A$247</definedName>
     <definedName name="MarketTable">'Market Data'!$A$2:$F$247</definedName>
+    <definedName name="DealNames">Deals!$B$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,7 +35,7 @@
     <numFmt numFmtId="170" formatCode="0_);\(0\)"/>
     <numFmt numFmtId="171" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -163,8 +163,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -233,8 +238,18 @@
         <fgColor rgb="001F3A5F"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -494,13 +509,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -770,6 +799,123 @@
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="6" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="12" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="12" fillId="6" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="12" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="6" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="6" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="6" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1921,10 +2067,7 @@
         <f>Deals!C2</f>
         <v/>
       </c>
-      <c r="J9" s="2">
-        <f>Deals!J1</f>
-        <v/>
-      </c>
+      <c r="J9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1944,10 +2087,7 @@
         <f>Deals!C3</f>
         <v/>
       </c>
-      <c r="J10" s="2">
-        <f>Deals!K1</f>
-        <v/>
-      </c>
+      <c r="J10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1967,10 +2107,7 @@
         <f>Deals!C5</f>
         <v/>
       </c>
-      <c r="J11" s="2">
-        <f>Deals!L1</f>
-        <v/>
-      </c>
+      <c r="J11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2598,8 +2735,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" prompt="Choose a deal to evaluate" type="list">
-      <formula1>$J$1:$J$11</formula1>
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>$J$1:$J$8</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2628,61 +2765,49 @@
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="120" t="inlineStr">
         <is>
           <t>Springfield (DST)</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="120" t="inlineStr">
         <is>
           <t>Hamburg (Dev)</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
-        <is>
-          <t>Maple Grove (Candidate)</t>
-        </is>
-      </c>
-      <c r="E1" s="17" t="inlineStr">
-        <is>
-          <t>armour</t>
-        </is>
-      </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="D1" s="120" t="inlineStr">
         <is>
           <t>Dev Model 11Mkts (MF)</t>
         </is>
       </c>
-      <c r="G1" s="17" t="inlineStr">
+      <c r="E1" s="120" t="inlineStr">
         <is>
           <t>Factory Model (Mfg)</t>
         </is>
       </c>
-      <c r="H1" s="17" t="inlineStr">
-        <is>
-          <t>[Comp] Winner (illustrative)</t>
-        </is>
-      </c>
-      <c r="I1" s="17" t="inlineStr">
-        <is>
-          <t>[Comp] Loser (illustrative)</t>
-        </is>
-      </c>
-      <c r="J1" s="17" t="inlineStr">
-        <is>
-          <t>New Deal 6</t>
-        </is>
-      </c>
-      <c r="K1" s="17" t="inlineStr">
-        <is>
-          <t>New Deal 7</t>
-        </is>
-      </c>
-      <c r="L1" s="17" t="inlineStr">
-        <is>
-          <t>New Deal 8</t>
-        </is>
-      </c>
+      <c r="F1" s="120" t="inlineStr">
+        <is>
+          <t>New Deal 1</t>
+        </is>
+      </c>
+      <c r="G1" s="120" t="inlineStr">
+        <is>
+          <t>New Deal 2</t>
+        </is>
+      </c>
+      <c r="H1" s="120" t="inlineStr">
+        <is>
+          <t>New Deal 3</t>
+        </is>
+      </c>
+      <c r="I1" s="120" t="inlineStr">
+        <is>
+          <t>New Deal 4</t>
+        </is>
+      </c>
+      <c r="J1" s="17" t="n"/>
+      <c r="K1" s="17" t="n"/>
+      <c r="L1" s="17" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
@@ -2690,61 +2815,49 @@
           <t>Deal type</t>
         </is>
       </c>
-      <c r="B2" s="34" t="inlineStr">
+      <c r="B2" s="121" t="inlineStr">
         <is>
           <t>Income/Core (DST/Stabilized)</t>
         </is>
       </c>
-      <c r="C2" s="34" t="inlineStr">
+      <c r="C2" s="121" t="inlineStr">
         <is>
           <t>Development</t>
         </is>
       </c>
-      <c r="D2" s="34" t="inlineStr">
+      <c r="D2" s="122" t="inlineStr">
         <is>
           <t>Development</t>
         </is>
       </c>
-      <c r="E2" s="19" t="inlineStr">
+      <c r="E2" s="123" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="F2" s="124" t="inlineStr">
         <is>
           <t>Income/Core (DST/Stabilized)</t>
         </is>
       </c>
-      <c r="F2" s="19" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="G2" s="35" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
-      </c>
-      <c r="H2" s="35" t="inlineStr">
+      <c r="G2" s="125" t="inlineStr">
         <is>
           <t>Income/Core (DST/Stabilized)</t>
         </is>
       </c>
-      <c r="I2" s="35" t="inlineStr">
+      <c r="H2" s="125" t="inlineStr">
         <is>
           <t>Income/Core (DST/Stabilized)</t>
         </is>
       </c>
-      <c r="J2" s="35" t="inlineStr">
+      <c r="I2" s="125" t="inlineStr">
         <is>
           <t>Income/Core (DST/Stabilized)</t>
         </is>
       </c>
-      <c r="K2" s="35" t="inlineStr">
-        <is>
-          <t>Income/Core (DST/Stabilized)</t>
-        </is>
-      </c>
-      <c r="L2" s="35" t="inlineStr">
-        <is>
-          <t>Income/Core (DST/Stabilized)</t>
-        </is>
-      </c>
+      <c r="J2" s="35" t="n"/>
+      <c r="K2" s="35" t="n"/>
+      <c r="L2" s="35" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
@@ -2752,42 +2865,30 @@
           <t>Market (county)</t>
         </is>
       </c>
-      <c r="B3" s="34" t="inlineStr">
+      <c r="B3" s="121" t="inlineStr">
         <is>
           <t>Springfield</t>
         </is>
       </c>
-      <c r="C3" s="34" t="inlineStr">
+      <c r="C3" s="121" t="inlineStr">
         <is>
           <t>Hamburg</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
-        <is>
-          <t>Nashville, Tennessee</t>
-        </is>
-      </c>
-      <c r="E3" s="19" t="n"/>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="D3" s="122" t="inlineStr">
         <is>
           <t>TX/OK/AR — workforce MF (placeholder mkt)</t>
         </is>
       </c>
-      <c r="G3" s="35" t="inlineStr">
+      <c r="E3" s="123" t="inlineStr">
         <is>
           <t>Modular factory — mfg business (placeholder mkt)</t>
         </is>
       </c>
-      <c r="H3" s="49" t="inlineStr">
-        <is>
-          <t>Illustrative strong storage market</t>
-        </is>
-      </c>
-      <c r="I3" s="49" t="inlineStr">
-        <is>
-          <t>Illustrative weak/overpaid deal</t>
-        </is>
-      </c>
+      <c r="F3" s="124" t="inlineStr"/>
+      <c r="G3" s="125" t="inlineStr"/>
+      <c r="H3" s="126" t="inlineStr"/>
+      <c r="I3" s="126" t="inlineStr"/>
       <c r="J3" s="35" t="n"/>
       <c r="K3" s="35" t="n"/>
       <c r="L3" s="35" t="n"/>
@@ -2798,47 +2899,37 @@
           <t>Is development (1/0)</t>
         </is>
       </c>
-      <c r="B4" s="36" t="n">
+      <c r="B4" s="127" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="36" t="n">
+      <c r="C4" s="127" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="36" t="n">
+      <c r="D4" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="37">
-        <f>IF(EXACT(E2,"Development"),1,0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="37">
+      <c r="E4" s="129" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="129">
         <f>IF(EXACT(F2,"Development"),1,0)</f>
         <v/>
       </c>
-      <c r="G4" s="38">
+      <c r="G4" s="130">
         <f>IF(EXACT(G2,"Development"),1,0)</f>
         <v/>
       </c>
-      <c r="H4" s="38">
+      <c r="H4" s="130">
         <f>IF(EXACT(H2,"Development"),1,0)</f>
         <v/>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="130">
         <f>IF(EXACT(I2,"Development"),1,0)</f>
         <v/>
       </c>
-      <c r="J4" s="38">
-        <f>IF(EXACT(J2,"Development"),1,0)</f>
-        <v/>
-      </c>
-      <c r="K4" s="38">
-        <f>IF(EXACT(K2,"Development"),1,0)</f>
-        <v/>
-      </c>
-      <c r="L4" s="38">
-        <f>IF(EXACT(L2,"Development"),1,0)</f>
-        <v/>
-      </c>
+      <c r="J4" s="38" t="n"/>
+      <c r="K4" s="38" t="n"/>
+      <c r="L4" s="38" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="21" t="inlineStr">
@@ -2846,28 +2937,22 @@
           <t>Total cost</t>
         </is>
       </c>
-      <c r="B5" s="39" t="n">
+      <c r="B5" s="131" t="n">
         <v>13212143</v>
       </c>
-      <c r="C5" s="39" t="n">
+      <c r="C5" s="131" t="n">
         <v>9592457</v>
       </c>
-      <c r="D5" s="39" t="n">
-        <v>9800000</v>
-      </c>
-      <c r="E5" s="22" t="n"/>
-      <c r="F5" s="22" t="n">
+      <c r="D5" s="132" t="n">
         <v>760660000</v>
       </c>
-      <c r="G5" s="40" t="n">
+      <c r="E5" s="133" t="n">
         <v>23500000</v>
       </c>
-      <c r="H5" s="40" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="I5" s="40" t="n">
-        <v>12000000</v>
-      </c>
+      <c r="F5" s="134" t="n"/>
+      <c r="G5" s="135" t="n"/>
+      <c r="H5" s="135" t="n"/>
+      <c r="I5" s="135" t="n"/>
       <c r="J5" s="40" t="n"/>
       <c r="K5" s="40" t="n"/>
       <c r="L5" s="40" t="n"/>
@@ -2878,28 +2963,22 @@
           <t>Equity</t>
         </is>
       </c>
-      <c r="B6" s="39" t="n">
+      <c r="B6" s="131" t="n">
         <v>13212143</v>
       </c>
-      <c r="C6" s="39" t="n">
+      <c r="C6" s="131" t="n">
         <v>5773999</v>
       </c>
-      <c r="D6" s="39" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="E6" s="22" t="n"/>
-      <c r="F6" s="22" t="n">
+      <c r="D6" s="132" t="n">
         <v>266231000</v>
       </c>
-      <c r="G6" s="40" t="n">
+      <c r="E6" s="133" t="n">
         <v>20000000</v>
       </c>
-      <c r="H6" s="40" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="I6" s="40" t="n">
-        <v>12000000</v>
-      </c>
+      <c r="F6" s="134" t="n"/>
+      <c r="G6" s="135" t="n"/>
+      <c r="H6" s="135" t="n"/>
+      <c r="I6" s="135" t="n"/>
       <c r="J6" s="40" t="n"/>
       <c r="K6" s="40" t="n"/>
       <c r="L6" s="40" t="n"/>
@@ -2910,28 +2989,22 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="B7" s="39" t="n">
+      <c r="B7" s="131" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="39" t="n">
+      <c r="C7" s="131" t="n">
         <v>3818458</v>
       </c>
-      <c r="D7" s="39" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n">
+      <c r="D7" s="132" t="n">
         <v>494429000</v>
       </c>
-      <c r="G7" s="40" t="n">
+      <c r="E7" s="133" t="n">
         <v>3500000</v>
       </c>
-      <c r="H7" s="50" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="I7" s="50" t="n">
-        <v>0</v>
-      </c>
+      <c r="F7" s="134" t="n"/>
+      <c r="G7" s="135" t="n"/>
+      <c r="H7" s="136" t="n"/>
+      <c r="I7" s="136" t="n"/>
       <c r="J7" s="40" t="n"/>
       <c r="K7" s="40" t="n"/>
       <c r="L7" s="40" t="n"/>
@@ -2942,47 +3015,37 @@
           <t>LTV</t>
         </is>
       </c>
-      <c r="B8" s="41" t="n">
+      <c r="B8" s="137" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="41" t="n">
+      <c r="C8" s="137" t="n">
         <v>0.3980688159456957</v>
       </c>
-      <c r="D8" s="41" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="E8" s="23">
-        <f>IFERROR(E7/E5,"")</f>
-        <v/>
-      </c>
-      <c r="F8" s="23">
+      <c r="D8" s="138" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E8" s="139" t="n">
+        <v>0.148936170212766</v>
+      </c>
+      <c r="F8" s="139">
         <f>IFERROR(F7/F5,"")</f>
         <v/>
       </c>
-      <c r="G8" s="42">
+      <c r="G8" s="140">
         <f>IFERROR(G7/G5,"")</f>
         <v/>
       </c>
-      <c r="H8" s="42">
+      <c r="H8" s="140">
         <f>IFERROR(H7/H5,"")</f>
         <v/>
       </c>
-      <c r="I8" s="42">
+      <c r="I8" s="140">
         <f>IFERROR(I7/I5,"")</f>
         <v/>
       </c>
-      <c r="J8" s="42">
-        <f>IFERROR(J7/J5,"")</f>
-        <v/>
-      </c>
-      <c r="K8" s="42">
-        <f>IFERROR(K7/K5,"")</f>
-        <v/>
-      </c>
-      <c r="L8" s="42">
-        <f>IFERROR(L7/L5,"")</f>
-        <v/>
-      </c>
+      <c r="J8" s="42" t="n"/>
+      <c r="K8" s="42" t="n"/>
+      <c r="L8" s="42" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
@@ -2990,20 +3053,16 @@
           <t>Going-in cap</t>
         </is>
       </c>
-      <c r="B9" s="41" t="n">
+      <c r="B9" s="137" t="n">
         <v>0.06999999924312052</v>
       </c>
-      <c r="C9" s="41" t="n"/>
-      <c r="D9" s="41" t="n"/>
-      <c r="E9" s="23" t="n"/>
-      <c r="F9" s="23" t="n"/>
-      <c r="G9" s="42" t="n"/>
-      <c r="H9" s="51" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="I9" s="51" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="C9" s="137" t="n"/>
+      <c r="D9" s="138" t="n"/>
+      <c r="E9" s="139" t="n"/>
+      <c r="F9" s="141" t="n"/>
+      <c r="G9" s="142" t="n"/>
+      <c r="H9" s="143" t="n"/>
+      <c r="I9" s="143" t="n"/>
       <c r="J9" s="42" t="n"/>
       <c r="K9" s="42" t="n"/>
       <c r="L9" s="42" t="n"/>
@@ -3014,28 +3073,22 @@
           <t>Exit cap</t>
         </is>
       </c>
-      <c r="B10" s="41" t="n">
+      <c r="B10" s="137" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C10" s="41" t="n">
+      <c r="C10" s="137" t="n">
         <v>0.055</v>
       </c>
-      <c r="D10" s="41" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E10" s="23" t="n"/>
-      <c r="F10" s="23" t="n">
+      <c r="D10" s="138" t="n">
         <v>0.0602</v>
       </c>
-      <c r="G10" s="42" t="n">
+      <c r="E10" s="139" t="n">
         <v>0.1</v>
       </c>
-      <c r="H10" s="51" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="I10" s="51" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="F10" s="141" t="n"/>
+      <c r="G10" s="142" t="n"/>
+      <c r="H10" s="143" t="n"/>
+      <c r="I10" s="143" t="n"/>
       <c r="J10" s="42" t="n"/>
       <c r="K10" s="42" t="n"/>
       <c r="L10" s="42" t="n"/>
@@ -3046,28 +3099,22 @@
           <t>NOI</t>
         </is>
       </c>
-      <c r="B11" s="39" t="n">
+      <c r="B11" s="131" t="n">
         <v>924850</v>
       </c>
-      <c r="C11" s="39" t="n">
+      <c r="C11" s="131" t="n">
         <v>706128.144158604</v>
       </c>
-      <c r="D11" s="39" t="n">
-        <v>735000</v>
-      </c>
-      <c r="E11" s="22" t="n"/>
-      <c r="F11" s="22" t="n">
+      <c r="D11" s="132" t="n">
         <v>58728924</v>
       </c>
-      <c r="G11" s="40" t="n">
+      <c r="E11" s="133" t="n">
         <v>11984000</v>
       </c>
-      <c r="H11" s="40" t="n">
-        <v>750000</v>
-      </c>
-      <c r="I11" s="40" t="n">
-        <v>600000</v>
-      </c>
+      <c r="F11" s="134" t="n"/>
+      <c r="G11" s="135" t="n"/>
+      <c r="H11" s="135" t="n"/>
+      <c r="I11" s="135" t="n"/>
       <c r="J11" s="40" t="n"/>
       <c r="K11" s="40" t="n"/>
       <c r="L11" s="40" t="n"/>
@@ -3078,28 +3125,22 @@
           <t>Op-ex ratio</t>
         </is>
       </c>
-      <c r="B12" s="41" t="n">
+      <c r="B12" s="137" t="n">
         <v>0.1401111621446224</v>
       </c>
-      <c r="C12" s="41" t="n">
+      <c r="C12" s="137" t="n">
         <v>0.3529709367265373</v>
       </c>
-      <c r="D12" s="41" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E12" s="23" t="n"/>
-      <c r="F12" s="23" t="n">
+      <c r="D12" s="138" t="n">
         <v>0.224</v>
       </c>
-      <c r="G12" s="42" t="n">
+      <c r="E12" s="139" t="n">
         <v>0.7</v>
       </c>
-      <c r="H12" s="42" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I12" s="42" t="n">
-        <v>0.45</v>
-      </c>
+      <c r="F12" s="141" t="n"/>
+      <c r="G12" s="142" t="n"/>
+      <c r="H12" s="142" t="n"/>
+      <c r="I12" s="142" t="n"/>
       <c r="J12" s="42" t="n"/>
       <c r="K12" s="42" t="n"/>
       <c r="L12" s="42" t="n"/>
@@ -3110,47 +3151,37 @@
           <t>Yield on cost</t>
         </is>
       </c>
-      <c r="B13" s="41" t="n">
+      <c r="B13" s="137" t="n">
         <v>0.06999999924312052</v>
       </c>
-      <c r="C13" s="41" t="n">
+      <c r="C13" s="137" t="n">
         <v>0.07361285478356629</v>
       </c>
-      <c r="D13" s="41" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E13" s="23">
-        <f>IFERROR(E11/E5,"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="23">
+      <c r="D13" s="138" t="n">
+        <v>0.07720785107669656</v>
+      </c>
+      <c r="E13" s="139" t="n">
+        <v>0.5099574468085106</v>
+      </c>
+      <c r="F13" s="139">
         <f>IFERROR(F11/F5,"")</f>
         <v/>
       </c>
-      <c r="G13" s="42">
+      <c r="G13" s="140">
         <f>IFERROR(G11/G5,"")</f>
         <v/>
       </c>
-      <c r="H13" s="42">
+      <c r="H13" s="140">
         <f>IFERROR(H11/H5,"")</f>
         <v/>
       </c>
-      <c r="I13" s="42">
+      <c r="I13" s="140">
         <f>IFERROR(I11/I5,"")</f>
         <v/>
       </c>
-      <c r="J13" s="42">
-        <f>IFERROR(J11/J5,"")</f>
-        <v/>
-      </c>
-      <c r="K13" s="42">
-        <f>IFERROR(K11/K5,"")</f>
-        <v/>
-      </c>
-      <c r="L13" s="42">
-        <f>IFERROR(L11/L5,"")</f>
-        <v/>
-      </c>
+      <c r="J13" s="42" t="n"/>
+      <c r="K13" s="42" t="n"/>
+      <c r="L13" s="42" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
@@ -3158,45 +3189,35 @@
           <t>Dev. spread</t>
         </is>
       </c>
-      <c r="B14" s="41" t="n"/>
-      <c r="C14" s="41" t="n">
+      <c r="B14" s="137" t="n"/>
+      <c r="C14" s="137" t="n">
         <v>0.01861285478356629</v>
       </c>
-      <c r="D14" s="41" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="E14" s="23">
-        <f>IF(AND(E4=1,E13&lt;&gt;"",E10&lt;&gt;""),E13-E10,"")</f>
-        <v/>
-      </c>
-      <c r="F14" s="23">
+      <c r="D14" s="138" t="n">
+        <v>0.01700785107669656</v>
+      </c>
+      <c r="E14" s="139" t="n">
+        <v>0.4099574468085107</v>
+      </c>
+      <c r="F14" s="139">
         <f>IF(AND(F4=1,F13&lt;&gt;"",F10&lt;&gt;""),F13-F10,"")</f>
         <v/>
       </c>
-      <c r="G14" s="42">
+      <c r="G14" s="140">
         <f>IF(AND(G4=1,G13&lt;&gt;"",G10&lt;&gt;""),G13-G10,"")</f>
         <v/>
       </c>
-      <c r="H14" s="42">
+      <c r="H14" s="140">
         <f>IF(AND(H4=1,H13&lt;&gt;"",H10&lt;&gt;""),H13-H10,"")</f>
         <v/>
       </c>
-      <c r="I14" s="42">
+      <c r="I14" s="140">
         <f>IF(AND(I4=1,I13&lt;&gt;"",I10&lt;&gt;""),I13-I10,"")</f>
         <v/>
       </c>
-      <c r="J14" s="42">
-        <f>IF(AND(J4=1,J13&lt;&gt;"",J10&lt;&gt;""),J13-J10,"")</f>
-        <v/>
-      </c>
-      <c r="K14" s="42">
-        <f>IF(AND(K4=1,K13&lt;&gt;"",K10&lt;&gt;""),K13-K10,"")</f>
-        <v/>
-      </c>
-      <c r="L14" s="42">
-        <f>IF(AND(L4=1,L13&lt;&gt;"",L10&lt;&gt;""),L13-L10,"")</f>
-        <v/>
-      </c>
+      <c r="J14" s="42" t="n"/>
+      <c r="K14" s="42" t="n"/>
+      <c r="L14" s="42" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="21" t="inlineStr">
@@ -3204,24 +3225,18 @@
           <t>Unlevered IRR</t>
         </is>
       </c>
-      <c r="B15" s="41" t="n">
+      <c r="B15" s="137" t="n">
         <v>0.1130438304475669</v>
       </c>
-      <c r="C15" s="41" t="n">
+      <c r="C15" s="137" t="n">
         <v>0.1731</v>
       </c>
-      <c r="D15" s="41" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="E15" s="23" t="n"/>
-      <c r="F15" s="23" t="n"/>
-      <c r="G15" s="42" t="n"/>
-      <c r="H15" s="51" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I15" s="51" t="n">
-        <v>0.045</v>
-      </c>
+      <c r="D15" s="138" t="n"/>
+      <c r="E15" s="139" t="n"/>
+      <c r="F15" s="141" t="n"/>
+      <c r="G15" s="142" t="n"/>
+      <c r="H15" s="143" t="n"/>
+      <c r="I15" s="143" t="n"/>
       <c r="J15" s="42" t="n"/>
       <c r="K15" s="42" t="n"/>
       <c r="L15" s="42" t="n"/>
@@ -3232,28 +3247,22 @@
           <t>Levered IRR</t>
         </is>
       </c>
-      <c r="B16" s="41" t="n">
+      <c r="B16" s="137" t="n">
         <v>0.1130438304475669</v>
       </c>
-      <c r="C16" s="41" t="n">
+      <c r="C16" s="137" t="n">
         <v>0.1691</v>
       </c>
-      <c r="D16" s="41" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="E16" s="23" t="n"/>
-      <c r="F16" s="23" t="n">
+      <c r="D16" s="138" t="n">
         <v>0.129</v>
       </c>
-      <c r="G16" s="42" t="n">
+      <c r="E16" s="139" t="n">
         <v>0.282</v>
       </c>
-      <c r="H16" s="51" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I16" s="51" t="n">
-        <v>0.045</v>
-      </c>
+      <c r="F16" s="141" t="n"/>
+      <c r="G16" s="142" t="n"/>
+      <c r="H16" s="143" t="n"/>
+      <c r="I16" s="143" t="n"/>
       <c r="J16" s="42" t="n"/>
       <c r="K16" s="42" t="n"/>
       <c r="L16" s="42" t="n"/>
@@ -3264,22 +3273,16 @@
           <t>NRSF</t>
         </is>
       </c>
-      <c r="B17" s="43" t="n"/>
-      <c r="C17" s="43" t="n">
+      <c r="B17" s="144" t="n"/>
+      <c r="C17" s="144" t="n">
         <v>63240</v>
       </c>
-      <c r="D17" s="43" t="n">
-        <v>78000</v>
-      </c>
-      <c r="E17" s="24" t="n"/>
-      <c r="F17" s="24" t="n"/>
-      <c r="G17" s="44" t="n"/>
-      <c r="H17" s="52" t="n">
-        <v>60000</v>
-      </c>
-      <c r="I17" s="44" t="n">
-        <v>57166</v>
-      </c>
+      <c r="D17" s="145" t="n"/>
+      <c r="E17" s="146" t="n"/>
+      <c r="F17" s="147" t="n"/>
+      <c r="G17" s="148" t="n"/>
+      <c r="H17" s="149" t="n"/>
+      <c r="I17" s="148" t="n"/>
       <c r="J17" s="44" t="n"/>
       <c r="K17" s="44" t="n"/>
       <c r="L17" s="44" t="n"/>
@@ -3290,18 +3293,16 @@
           <t>Site acreage</t>
         </is>
       </c>
-      <c r="B18" s="43" t="n"/>
-      <c r="C18" s="43" t="n">
+      <c r="B18" s="144" t="n"/>
+      <c r="C18" s="144" t="n">
         <v>11.16</v>
       </c>
-      <c r="D18" s="43" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="E18" s="24" t="n"/>
-      <c r="F18" s="24" t="n"/>
-      <c r="G18" s="44" t="n"/>
-      <c r="H18" s="44" t="n"/>
-      <c r="I18" s="44" t="n"/>
+      <c r="D18" s="145" t="n"/>
+      <c r="E18" s="146" t="n"/>
+      <c r="F18" s="147" t="n"/>
+      <c r="G18" s="148" t="n"/>
+      <c r="H18" s="148" t="n"/>
+      <c r="I18" s="148" t="n"/>
       <c r="J18" s="44" t="n"/>
       <c r="K18" s="44" t="n"/>
       <c r="L18" s="44" t="n"/>
@@ -3312,22 +3313,20 @@
           <t>Units</t>
         </is>
       </c>
-      <c r="B19" s="43" t="n"/>
-      <c r="C19" s="43" t="n">
+      <c r="B19" s="144" t="n"/>
+      <c r="C19" s="144" t="n">
         <v>542</v>
       </c>
-      <c r="D19" s="43" t="n">
-        <v>560</v>
-      </c>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="24" t="n">
+      <c r="D19" s="145" t="n">
         <v>3300</v>
       </c>
-      <c r="G19" s="44" t="n">
+      <c r="E19" s="146" t="n">
         <v>700</v>
       </c>
-      <c r="H19" s="44" t="n"/>
-      <c r="I19" s="44" t="n"/>
+      <c r="F19" s="147" t="n"/>
+      <c r="G19" s="148" t="n"/>
+      <c r="H19" s="148" t="n"/>
+      <c r="I19" s="148" t="n"/>
       <c r="J19" s="44" t="n"/>
       <c r="K19" s="44" t="n"/>
       <c r="L19" s="44" t="n"/>
@@ -3338,16 +3337,16 @@
           <t>Avg rate $/NRSF</t>
         </is>
       </c>
-      <c r="B20" s="45" t="n"/>
-      <c r="C20" s="45" t="n">
+      <c r="B20" s="150" t="n"/>
+      <c r="C20" s="150" t="n">
         <v>16.74763438488299</v>
       </c>
-      <c r="D20" s="45" t="n"/>
-      <c r="E20" s="46" t="n"/>
-      <c r="F20" s="46" t="n"/>
-      <c r="G20" s="47" t="n"/>
-      <c r="H20" s="47" t="n"/>
-      <c r="I20" s="47" t="n"/>
+      <c r="D20" s="151" t="n"/>
+      <c r="E20" s="152" t="n"/>
+      <c r="F20" s="153" t="n"/>
+      <c r="G20" s="154" t="n"/>
+      <c r="H20" s="154" t="n"/>
+      <c r="I20" s="154" t="n"/>
       <c r="J20" s="47" t="n"/>
       <c r="K20" s="47" t="n"/>
       <c r="L20" s="47" t="n"/>
@@ -3358,43 +3357,37 @@
           <t>Market population</t>
         </is>
       </c>
-      <c r="B21" s="43" t="n">
+      <c r="B21" s="144" t="n">
         <v>250000</v>
       </c>
-      <c r="C21" s="43" t="n">
+      <c r="C21" s="144" t="n">
         <v>250000</v>
       </c>
-      <c r="D21" s="43" t="n">
-        <v>269136</v>
-      </c>
-      <c r="E21" s="24">
-        <f>IFERROR(VLOOKUP(E3,MarketTable,2,FALSE),"")</f>
+      <c r="D21" s="145" t="n">
+        <v>250000</v>
+      </c>
+      <c r="E21" s="146" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F21" s="146">
+        <f>IFERROR(VLOOKUP(F3,MarketTable,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F21" s="24" t="n">
-        <v>250000</v>
-      </c>
-      <c r="G21" s="44" t="n">
-        <v>250000</v>
-      </c>
-      <c r="H21" s="52" t="n">
-        <v>260000</v>
-      </c>
-      <c r="I21" s="52" t="n">
-        <v>150000</v>
-      </c>
-      <c r="J21" s="44">
-        <f>IFERROR(VLOOKUP(J3,MarketTable,2,FALSE),"")</f>
+      <c r="G21" s="155">
+        <f>IFERROR(VLOOKUP(G3,MarketTable,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="K21" s="44">
-        <f>IFERROR(VLOOKUP(K3,MarketTable,2,FALSE),"")</f>
+      <c r="H21" s="156">
+        <f>IFERROR(VLOOKUP(H3,MarketTable,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L21" s="44">
-        <f>IFERROR(VLOOKUP(L3,MarketTable,2,FALSE),"")</f>
+      <c r="I21" s="156">
+        <f>IFERROR(VLOOKUP(I3,MarketTable,2,FALSE),"")</f>
         <v/>
       </c>
+      <c r="J21" s="44" t="n"/>
+      <c r="K21" s="44" t="n"/>
+      <c r="L21" s="44" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
@@ -3402,43 +3395,37 @@
           <t>5-yr pop growth</t>
         </is>
       </c>
-      <c r="B22" s="41" t="n">
+      <c r="B22" s="137" t="n">
         <v>0.06</v>
       </c>
-      <c r="C22" s="41" t="n">
+      <c r="C22" s="137" t="n">
         <v>0.06</v>
       </c>
-      <c r="D22" s="41" t="n">
-        <v>0.01955002884430485</v>
-      </c>
-      <c r="E22" s="23">
-        <f>IFERROR(VLOOKUP(E3,MarketTable,3,FALSE),"")</f>
+      <c r="D22" s="138" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E22" s="139" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F22" s="139">
+        <f>IFERROR(VLOOKUP(F3,MarketTable,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F22" s="23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G22" s="42" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H22" s="51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I22" s="51" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="J22" s="42">
-        <f>IFERROR(VLOOKUP(J3,MarketTable,3,FALSE),"")</f>
+      <c r="G22" s="140">
+        <f>IFERROR(VLOOKUP(G3,MarketTable,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="K22" s="42">
-        <f>IFERROR(VLOOKUP(K3,MarketTable,3,FALSE),"")</f>
+      <c r="H22" s="157">
+        <f>IFERROR(VLOOKUP(H3,MarketTable,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L22" s="42">
-        <f>IFERROR(VLOOKUP(L3,MarketTable,3,FALSE),"")</f>
+      <c r="I22" s="157">
+        <f>IFERROR(VLOOKUP(I3,MarketTable,3,FALSE),"")</f>
         <v/>
       </c>
+      <c r="J22" s="42" t="n"/>
+      <c r="K22" s="42" t="n"/>
+      <c r="L22" s="42" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
@@ -3446,43 +3433,37 @@
           <t>Supply pipeline %</t>
         </is>
       </c>
-      <c r="B23" s="41" t="n">
+      <c r="B23" s="137" t="n">
         <v>0.04</v>
       </c>
-      <c r="C23" s="41" t="n">
+      <c r="C23" s="137" t="n">
         <v>0.04</v>
       </c>
-      <c r="D23" s="41" t="n">
-        <v>0.09363192916145506</v>
-      </c>
-      <c r="E23" s="23">
-        <f>IFERROR(VLOOKUP(E3,MarketTable,4,FALSE),"")</f>
+      <c r="D23" s="138" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E23" s="139" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F23" s="139">
+        <f>IFERROR(VLOOKUP(F3,MarketTable,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F23" s="23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G23" s="42" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H23" s="51" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I23" s="51" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J23" s="42">
-        <f>IFERROR(VLOOKUP(J3,MarketTable,4,FALSE),"")</f>
+      <c r="G23" s="140">
+        <f>IFERROR(VLOOKUP(G3,MarketTable,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="K23" s="42">
-        <f>IFERROR(VLOOKUP(K3,MarketTable,4,FALSE),"")</f>
+      <c r="H23" s="157">
+        <f>IFERROR(VLOOKUP(H3,MarketTable,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L23" s="42">
-        <f>IFERROR(VLOOKUP(L3,MarketTable,4,FALSE),"")</f>
+      <c r="I23" s="157">
+        <f>IFERROR(VLOOKUP(I3,MarketTable,4,FALSE),"")</f>
         <v/>
       </c>
+      <c r="J23" s="42" t="n"/>
+      <c r="K23" s="42" t="n"/>
+      <c r="L23" s="42" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="21" t="inlineStr">
@@ -3490,35 +3471,29 @@
           <t>Market rank</t>
         </is>
       </c>
-      <c r="B24" s="36" t="n"/>
-      <c r="C24" s="36" t="n"/>
-      <c r="D24" s="36" t="n">
-        <v>23</v>
-      </c>
-      <c r="E24" s="37">
-        <f>IFERROR(VLOOKUP(E3,MarketTable,5,FALSE),"")</f>
+      <c r="B24" s="127" t="n"/>
+      <c r="C24" s="127" t="n"/>
+      <c r="D24" s="128" t="n"/>
+      <c r="E24" s="129" t="n"/>
+      <c r="F24" s="129">
+        <f>IFERROR(VLOOKUP(F3,MarketTable,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F24" s="37" t="n"/>
-      <c r="G24" s="38" t="n"/>
-      <c r="H24" s="38" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="38" t="n">
-        <v>220</v>
-      </c>
-      <c r="J24" s="38">
-        <f>IFERROR(VLOOKUP(J3,MarketTable,5,FALSE),"")</f>
+      <c r="G24" s="130">
+        <f>IFERROR(VLOOKUP(G3,MarketTable,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="K24" s="38">
-        <f>IFERROR(VLOOKUP(K3,MarketTable,5,FALSE),"")</f>
+      <c r="H24" s="130">
+        <f>IFERROR(VLOOKUP(H3,MarketTable,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L24" s="38">
-        <f>IFERROR(VLOOKUP(L3,MarketTable,5,FALSE),"")</f>
+      <c r="I24" s="130">
+        <f>IFERROR(VLOOKUP(I3,MarketTable,5,FALSE),"")</f>
         <v/>
       </c>
+      <c r="J24" s="38" t="n"/>
+      <c r="K24" s="38" t="n"/>
+      <c r="L24" s="38" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="21" t="inlineStr">
@@ -3526,35 +3501,29 @@
           <t>Market weighted score</t>
         </is>
       </c>
-      <c r="B25" s="45" t="n"/>
-      <c r="C25" s="45" t="n"/>
-      <c r="D25" s="45" t="n">
-        <v>0.5725815198758409</v>
-      </c>
-      <c r="E25" s="46">
-        <f>IFERROR(VLOOKUP(E3,MarketTable,6,FALSE),"")</f>
+      <c r="B25" s="150" t="n"/>
+      <c r="C25" s="150" t="n"/>
+      <c r="D25" s="151" t="n"/>
+      <c r="E25" s="152" t="n"/>
+      <c r="F25" s="152">
+        <f>IFERROR(VLOOKUP(F3,MarketTable,6,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F25" s="46" t="n"/>
-      <c r="G25" s="47" t="n"/>
-      <c r="H25" s="47" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I25" s="47" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J25" s="47">
-        <f>IFERROR(VLOOKUP(J3,MarketTable,6,FALSE),"")</f>
+      <c r="G25" s="158">
+        <f>IFERROR(VLOOKUP(G3,MarketTable,6,FALSE),"")</f>
         <v/>
       </c>
-      <c r="K25" s="47">
-        <f>IFERROR(VLOOKUP(K3,MarketTable,6,FALSE),"")</f>
+      <c r="H25" s="158">
+        <f>IFERROR(VLOOKUP(H3,MarketTable,6,FALSE),"")</f>
         <v/>
       </c>
-      <c r="L25" s="47">
-        <f>IFERROR(VLOOKUP(L3,MarketTable,6,FALSE),"")</f>
+      <c r="I25" s="158">
+        <f>IFERROR(VLOOKUP(I3,MarketTable,6,FALSE),"")</f>
         <v/>
       </c>
+      <c r="J25" s="47" t="n"/>
+      <c r="K25" s="47" t="n"/>
+      <c r="L25" s="47" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
@@ -3562,50 +3531,41 @@
           <t>Best IRR (calc)</t>
         </is>
       </c>
-      <c r="B26" s="41">
+      <c r="B26" s="138">
         <f>IF(COUNT(B15:B16)=0,"",MAX(B15:B16))</f>
         <v/>
       </c>
-      <c r="C26" s="41">
+      <c r="C26" s="138">
         <f>IF(COUNT(C15:C16)=0,"",MAX(C15:C16))</f>
         <v/>
       </c>
-      <c r="D26" s="41">
+      <c r="D26" s="138">
         <f>IF(COUNT(D15:D16)=0,"",MAX(D15:D16))</f>
         <v/>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="139">
         <f>IF(COUNT(E15:E16)=0,"",MAX(E15:E16))</f>
         <v/>
       </c>
-      <c r="F26" s="23">
+      <c r="F26" s="139">
         <f>IF(COUNT(F15:F16)=0,"",MAX(F15:F16))</f>
         <v/>
       </c>
-      <c r="G26" s="42">
+      <c r="G26" s="140">
         <f>IF(COUNT(G15:G16)=0,"",MAX(G15:G16))</f>
         <v/>
       </c>
-      <c r="H26" s="42">
+      <c r="H26" s="140">
         <f>IF(COUNT(H15:H16)=0,"",MAX(H15:H16))</f>
         <v/>
       </c>
-      <c r="I26" s="42">
+      <c r="I26" s="140">
         <f>IF(COUNT(I15:I16)=0,"",MAX(I15:I16))</f>
         <v/>
       </c>
-      <c r="J26" s="42">
-        <f>IF(COUNT(J15:J16)=0,"",MAX(J15:J16))</f>
-        <v/>
-      </c>
-      <c r="K26" s="42">
-        <f>IF(COUNT(K15:K16)=0,"",MAX(K15:K16))</f>
-        <v/>
-      </c>
-      <c r="L26" s="42">
-        <f>IF(COUNT(L15:L16)=0,"",MAX(L15:L16))</f>
-        <v/>
-      </c>
+      <c r="J26" s="42" t="n"/>
+      <c r="K26" s="42" t="n"/>
+      <c r="L26" s="42" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="21" t="inlineStr">
@@ -3613,57 +3573,66 @@
           <t>Underwriting yield (calc)</t>
         </is>
       </c>
-      <c r="B27" s="41">
+      <c r="B27" s="138">
         <f>IF(B4=1,B13,B9)</f>
         <v/>
       </c>
-      <c r="C27" s="41">
+      <c r="C27" s="138">
         <f>IF(C4=1,C13,C9)</f>
         <v/>
       </c>
-      <c r="D27" s="41">
+      <c r="D27" s="138">
         <f>IF(D4=1,D13,D9)</f>
         <v/>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="139">
         <f>IF(E4=1,E13,E9)</f>
         <v/>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="139">
         <f>IF(F4=1,F13,F9)</f>
         <v/>
       </c>
-      <c r="G27" s="42">
+      <c r="G27" s="140">
         <f>IF(G4=1,G13,G9)</f>
         <v/>
       </c>
-      <c r="H27" s="42">
+      <c r="H27" s="140">
         <f>IF(H4=1,H13,H9)</f>
         <v/>
       </c>
-      <c r="I27" s="42">
+      <c r="I27" s="140">
         <f>IF(I4=1,I13,I9)</f>
         <v/>
       </c>
-      <c r="J27" s="42">
-        <f>IF(J4=1,J13,J9)</f>
-        <v/>
-      </c>
-      <c r="K27" s="42">
-        <f>IF(K4=1,K13,K9)</f>
-        <v/>
-      </c>
-      <c r="L27" s="42">
-        <f>IF(L4=1,L13,L9)</f>
-        <v/>
-      </c>
+      <c r="J27" s="42" t="n"/>
+      <c r="K27" s="42" t="n"/>
+      <c r="L27" s="42" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="E2:L2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+  <dataValidations count="8">
+    <dataValidation sqref="F2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Income/Core (DST/Stabilized),Development"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:L3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="Pick the deal's county" type="list">
+    <dataValidation sqref="F3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="Pick the deal's county" type="list">
+      <formula1>MarketCounties</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Income/Core (DST/Stabilized),Development"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="Pick the deal's county" type="list">
+      <formula1>MarketCounties</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Income/Core (DST/Stabilized),Development"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="Pick the deal's county" type="list">
+      <formula1>MarketCounties</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Income/Core (DST/Stabilized),Development"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="Pick the deal's county" type="list">
       <formula1>MarketCounties</formula1>
     </dataValidation>
   </dataValidations>
@@ -3732,18 +3701,9 @@
         <f>Deals!I1</f>
         <v/>
       </c>
-      <c r="J1" s="9">
-        <f>Deals!J1</f>
-        <v/>
-      </c>
-      <c r="K1" s="9">
-        <f>Deals!K1</f>
-        <v/>
-      </c>
-      <c r="L1" s="9">
-        <f>Deals!L1</f>
-        <v/>
-      </c>
+      <c r="J1" s="9" t="n"/>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -3783,18 +3743,9 @@
         <f>IF(OR(Deals!I26="",Deals!I10=""),0,IF(Deals!I26&gt;Deals!I10,15,0))</f>
         <v/>
       </c>
-      <c r="J2" s="10">
-        <f>IF(OR(Deals!J26="",Deals!J10=""),0,IF(Deals!J26&gt;Deals!J10,15,0))</f>
-        <v/>
-      </c>
-      <c r="K2" s="10">
-        <f>IF(OR(Deals!K26="",Deals!K10=""),0,IF(Deals!K26&gt;Deals!K10,15,0))</f>
-        <v/>
-      </c>
-      <c r="L2" s="10">
-        <f>IF(OR(Deals!L26="",Deals!L10=""),0,IF(Deals!L26&gt;Deals!L10,15,0))</f>
-        <v/>
-      </c>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3834,18 +3785,9 @@
         <f>IF(Deals!I27="",0,IF(Deals!I27&gt;=0.075,15,IF(Deals!I27&gt;=0.065,7.5,0)))</f>
         <v/>
       </c>
-      <c r="J3" s="10">
-        <f>IF(Deals!J27="",0,IF(Deals!J27&gt;=0.075,15,IF(Deals!J27&gt;=0.065,7.5,0)))</f>
-        <v/>
-      </c>
-      <c r="K3" s="10">
-        <f>IF(Deals!K27="",0,IF(Deals!K27&gt;=0.075,15,IF(Deals!K27&gt;=0.065,7.5,0)))</f>
-        <v/>
-      </c>
-      <c r="L3" s="10">
-        <f>IF(Deals!L27="",0,IF(Deals!L27&gt;=0.075,15,IF(Deals!L27&gt;=0.065,7.5,0)))</f>
-        <v/>
-      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -3885,18 +3827,9 @@
         <f>IF(Deals!I12="",0,IF(Deals!I12&lt;=0.3,10,IF(Deals!I12&lt;=0.35,5,0)))</f>
         <v/>
       </c>
-      <c r="J4" s="10">
-        <f>IF(Deals!J12="",0,IF(Deals!J12&lt;=0.3,10,IF(Deals!J12&lt;=0.35,5,0)))</f>
-        <v/>
-      </c>
-      <c r="K4" s="10">
-        <f>IF(Deals!K12="",0,IF(Deals!K12&lt;=0.3,10,IF(Deals!K12&lt;=0.35,5,0)))</f>
-        <v/>
-      </c>
-      <c r="L4" s="10">
-        <f>IF(Deals!L12="",0,IF(Deals!L12&lt;=0.3,10,IF(Deals!L12&lt;=0.35,5,0)))</f>
-        <v/>
-      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3936,18 +3869,9 @@
         <f>IF(Deals!I21="",0,IF(Deals!I21&gt;=200000,12,0))</f>
         <v/>
       </c>
-      <c r="J5" s="10">
-        <f>IF(Deals!J21="",0,IF(Deals!J21&gt;=200000,12,0))</f>
-        <v/>
-      </c>
-      <c r="K5" s="10">
-        <f>IF(Deals!K21="",0,IF(Deals!K21&gt;=200000,12,0))</f>
-        <v/>
-      </c>
-      <c r="L5" s="10">
-        <f>IF(Deals!L21="",0,IF(Deals!L21&gt;=200000,12,0))</f>
-        <v/>
-      </c>
+      <c r="J5" s="10" t="n"/>
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -3987,18 +3911,9 @@
         <f>IF(Deals!I22="",5,IF(Deals!I22&gt;=0.05,10,IF(Deals!I22&gt;0,5,0)))</f>
         <v/>
       </c>
-      <c r="J6" s="10">
-        <f>IF(Deals!J22="",5,IF(Deals!J22&gt;=0.05,10,IF(Deals!J22&gt;0,5,0)))</f>
-        <v/>
-      </c>
-      <c r="K6" s="10">
-        <f>IF(Deals!K22="",5,IF(Deals!K22&gt;=0.05,10,IF(Deals!K22&gt;0,5,0)))</f>
-        <v/>
-      </c>
-      <c r="L6" s="10">
-        <f>IF(Deals!L22="",5,IF(Deals!L22&gt;=0.05,10,IF(Deals!L22&gt;0,5,0)))</f>
-        <v/>
-      </c>
+      <c r="J6" s="10" t="n"/>
+      <c r="K6" s="10" t="n"/>
+      <c r="L6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -4038,18 +3953,9 @@
         <f>IF(Deals!I23="",5,IF(Deals!I23&lt;=0.05,10,IF(Deals!I23&lt;=0.1,5,0)))</f>
         <v/>
       </c>
-      <c r="J7" s="10">
-        <f>IF(Deals!J23="",5,IF(Deals!J23&lt;=0.05,10,IF(Deals!J23&lt;=0.1,5,0)))</f>
-        <v/>
-      </c>
-      <c r="K7" s="10">
-        <f>IF(Deals!K23="",5,IF(Deals!K23&lt;=0.05,10,IF(Deals!K23&lt;=0.1,5,0)))</f>
-        <v/>
-      </c>
-      <c r="L7" s="10">
-        <f>IF(Deals!L23="",5,IF(Deals!L23&lt;=0.05,10,IF(Deals!L23&lt;=0.1,5,0)))</f>
-        <v/>
-      </c>
+      <c r="J7" s="10" t="n"/>
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -4089,18 +3995,9 @@
         <f>IF(Deals!I26="",0,IF(Deals!I26&gt;=IF(Deals!I4=1,0.15,0.1),13,IF(Deals!I26&gt;=IF(Deals!I4=1,0.12,0.07),6.5,0)))</f>
         <v/>
       </c>
-      <c r="J8" s="10">
-        <f>IF(Deals!J26="",0,IF(Deals!J26&gt;=IF(Deals!J4=1,0.15,0.1),13,IF(Deals!J26&gt;=IF(Deals!J4=1,0.12,0.07),6.5,0)))</f>
-        <v/>
-      </c>
-      <c r="K8" s="10">
-        <f>IF(Deals!K26="",0,IF(Deals!K26&gt;=IF(Deals!K4=1,0.15,0.1),13,IF(Deals!K26&gt;=IF(Deals!K4=1,0.12,0.07),6.5,0)))</f>
-        <v/>
-      </c>
-      <c r="L8" s="10">
-        <f>IF(Deals!L26="",0,IF(Deals!L26&gt;=IF(Deals!L4=1,0.15,0.1),13,IF(Deals!L26&gt;=IF(Deals!L4=1,0.12,0.07),6.5,0)))</f>
-        <v/>
-      </c>
+      <c r="J8" s="10" t="n"/>
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -4140,18 +4037,9 @@
         <f>IF(Deals!I24="",4,IF(Deals!I24&lt;=123,8,IF(Deals!I24&lt;=184,4,0)))</f>
         <v/>
       </c>
-      <c r="J9" s="10">
-        <f>IF(Deals!J24="",4,IF(Deals!J24&lt;=123,8,IF(Deals!J24&lt;=184,4,0)))</f>
-        <v/>
-      </c>
-      <c r="K9" s="10">
-        <f>IF(Deals!K24="",4,IF(Deals!K24&lt;=123,8,IF(Deals!K24&lt;=184,4,0)))</f>
-        <v/>
-      </c>
-      <c r="L9" s="10">
-        <f>IF(Deals!L24="",4,IF(Deals!L24&lt;=123,8,IF(Deals!L24&lt;=184,4,0)))</f>
-        <v/>
-      </c>
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -4191,19 +4079,11 @@
         <f>IF(Deals!I17="",3.5,IF(AND(Deals!I17&gt;=40000,Deals!I17&lt;=120000),7,IF(AND(Deals!I17&gt;=25000,Deals!I17&lt;=150000),3.5,0)))</f>
         <v/>
       </c>
-      <c r="J10" s="10">
-        <f>IF(Deals!J17="",3.5,IF(AND(Deals!J17&gt;=40000,Deals!J17&lt;=120000),7,IF(AND(Deals!J17&gt;=25000,Deals!J17&lt;=150000),3.5,0)))</f>
-        <v/>
-      </c>
-      <c r="K10" s="10">
-        <f>IF(Deals!K17="",3.5,IF(AND(Deals!K17&gt;=40000,Deals!K17&lt;=120000),7,IF(AND(Deals!K17&gt;=25000,Deals!K17&lt;=150000),3.5,0)))</f>
-        <v/>
-      </c>
-      <c r="L10" s="10">
-        <f>IF(Deals!L17="",3.5,IF(AND(Deals!L17&gt;=40000,Deals!L17&lt;=120000),7,IF(AND(Deals!L17&gt;=25000,Deals!L17&lt;=150000),3.5,0)))</f>
-        <v/>
-      </c>
-    </row>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -4242,18 +4122,9 @@
         <f>SUM(I2:I10)</f>
         <v/>
       </c>
-      <c r="J12" s="7">
-        <f>SUM(J2:J10)</f>
-        <v/>
-      </c>
-      <c r="K12" s="7">
-        <f>SUM(K2:K10)</f>
-        <v/>
-      </c>
-      <c r="L12" s="7">
-        <f>SUM(L2:L10)</f>
-        <v/>
-      </c>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -4293,18 +4164,9 @@
         <f>IF(OR(IF(OR(Deals!I26="",Deals!I10=""),1,IF(Deals!I26&gt;Deals!I10,0,1))=1,IF(Deals!I27="",1,IF(Deals!I27&gt;=0.065,0,1))=1,IF(Deals!I21="",1,IF(Deals!I21&gt;=200000,0,1))=1),1,0)</f>
         <v/>
       </c>
-      <c r="J13" s="10">
-        <f>IF(OR(IF(OR(Deals!J26="",Deals!J10=""),1,IF(Deals!J26&gt;Deals!J10,0,1))=1,IF(Deals!J27="",1,IF(Deals!J27&gt;=0.065,0,1))=1,IF(Deals!J21="",1,IF(Deals!J21&gt;=200000,0,1))=1),1,0)</f>
-        <v/>
-      </c>
-      <c r="K13" s="10">
-        <f>IF(OR(IF(OR(Deals!K26="",Deals!K10=""),1,IF(Deals!K26&gt;Deals!K10,0,1))=1,IF(Deals!K27="",1,IF(Deals!K27&gt;=0.065,0,1))=1,IF(Deals!K21="",1,IF(Deals!K21&gt;=200000,0,1))=1),1,0)</f>
-        <v/>
-      </c>
-      <c r="L13" s="10">
-        <f>IF(OR(IF(OR(Deals!L26="",Deals!L10=""),1,IF(Deals!L26&gt;Deals!L10,0,1))=1,IF(Deals!L27="",1,IF(Deals!L27&gt;=0.065,0,1))=1,IF(Deals!L21="",1,IF(Deals!L21&gt;=200000,0,1))=1),1,0)</f>
-        <v/>
-      </c>
+      <c r="J13" s="10" t="n"/>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -4344,18 +4206,9 @@
         <f>IF(I13=1,"NO-GO",IF(I12&gt;=70,"GO",IF(I12&gt;=50,"CONDITIONAL GO","NO-GO")))</f>
         <v/>
       </c>
-      <c r="J14" s="7">
-        <f>IF(J13=1,"NO-GO",IF(J12&gt;=70,"GO",IF(J12&gt;=50,"CONDITIONAL GO","NO-GO")))</f>
-        <v/>
-      </c>
-      <c r="K14" s="7">
-        <f>IF(K13=1,"NO-GO",IF(K12&gt;=70,"GO",IF(K12&gt;=50,"CONDITIONAL GO","NO-GO")))</f>
-        <v/>
-      </c>
-      <c r="L14" s="7">
-        <f>IF(L13=1,"NO-GO",IF(L12&gt;=70,"GO",IF(L12&gt;=50,"CONDITIONAL GO","NO-GO")))</f>
-        <v/>
-      </c>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B14:L14">
@@ -4421,10 +4274,9 @@
         <f>Deals!B1</f>
         <v/>
       </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>Income/Core (DST/Stabilized)</t>
-        </is>
+      <c r="B4" s="18">
+        <f>Deals!B2</f>
+        <v/>
       </c>
       <c r="C4" s="19">
         <f>Scores!B12</f>
@@ -4440,10 +4292,9 @@
         <f>Deals!C1</f>
         <v/>
       </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
+      <c r="B5" s="18">
+        <f>Deals!C2</f>
+        <v/>
       </c>
       <c r="C5" s="19">
         <f>Scores!C12</f>
@@ -4459,10 +4310,9 @@
         <f>Deals!D1</f>
         <v/>
       </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>Development</t>
-        </is>
+      <c r="B6" s="18">
+        <f>Deals!D2</f>
+        <v/>
       </c>
       <c r="C6" s="19">
         <f>Scores!D12</f>
@@ -4564,58 +4414,22 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18">
-        <f>Deals!J1</f>
-        <v/>
-      </c>
-      <c r="B12" s="18">
-        <f>Deals!J2</f>
-        <v/>
-      </c>
-      <c r="C12" s="19">
-        <f>Scores!J12</f>
-        <v/>
-      </c>
-      <c r="D12" s="20">
-        <f>Scores!J14</f>
-        <v/>
-      </c>
+      <c r="A12" s="18" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="20" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18">
-        <f>Deals!K1</f>
-        <v/>
-      </c>
-      <c r="B13" s="18">
-        <f>Deals!K2</f>
-        <v/>
-      </c>
-      <c r="C13" s="19">
-        <f>Scores!K12</f>
-        <v/>
-      </c>
-      <c r="D13" s="20">
-        <f>Scores!K14</f>
-        <v/>
-      </c>
+      <c r="A13" s="18" t="n"/>
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="20" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18">
-        <f>Deals!L1</f>
-        <v/>
-      </c>
-      <c r="B14" s="18">
-        <f>Deals!L2</f>
-        <v/>
-      </c>
-      <c r="C14" s="19">
-        <f>Scores!L12</f>
-        <v/>
-      </c>
-      <c r="D14" s="20">
-        <f>Scores!L14</f>
-        <v/>
-      </c>
+      <c r="A14" s="18" t="n"/>
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="20" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D4:D14">

--- a/ICGoNoGoDashboard_Working.xlsx
+++ b/ICGoNoGoDashboard_Working.xlsx
@@ -529,7 +529,7 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -915,6 +915,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="12" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1927,7 +1948,8 @@
     <col width="32.453125" customWidth="1" style="54" min="2" max="2"/>
     <col width="26.54296875" bestFit="1" customWidth="1" style="54" min="3" max="3"/>
     <col width="13.7265625" bestFit="1" customWidth="1" style="54" min="4" max="4"/>
-    <col width="19" customWidth="1" style="54" min="5" max="5"/>
+    <col width="20" customWidth="1" style="54" min="5" max="5"/>
+    <col width="18" customWidth="1" style="54" min="6" max="6"/>
     <col hidden="1" width="13" customWidth="1" style="54" min="8" max="8"/>
     <col hidden="1" width="13" customWidth="1" style="54" min="10" max="10"/>
   </cols>
@@ -2044,6 +2066,14 @@
         <f>Deals!C1</f>
         <v/>
       </c>
+      <c r="E8" s="120">
+        <f>Deals!D1</f>
+        <v/>
+      </c>
+      <c r="F8" s="120">
+        <f>Deals!E1</f>
+        <v/>
+      </c>
       <c r="J8" s="2">
         <f>Deals!I1</f>
         <v/>
@@ -2067,6 +2097,14 @@
         <f>Deals!C2</f>
         <v/>
       </c>
+      <c r="E9" s="123">
+        <f>Deals!D2</f>
+        <v/>
+      </c>
+      <c r="F9" s="123">
+        <f>Deals!E2</f>
+        <v/>
+      </c>
       <c r="J9" s="2" t="n"/>
     </row>
     <row r="10">
@@ -2087,6 +2125,14 @@
         <f>Deals!C3</f>
         <v/>
       </c>
+      <c r="E10" s="123">
+        <f>Deals!D3</f>
+        <v/>
+      </c>
+      <c r="F10" s="123">
+        <f>Deals!E3</f>
+        <v/>
+      </c>
       <c r="J10" s="2" t="n"/>
     </row>
     <row r="11">
@@ -2107,6 +2153,14 @@
         <f>Deals!C5</f>
         <v/>
       </c>
+      <c r="E11" s="159">
+        <f>Deals!D5</f>
+        <v/>
+      </c>
+      <c r="F11" s="159">
+        <f>Deals!E5</f>
+        <v/>
+      </c>
       <c r="J11" s="2" t="n"/>
     </row>
     <row r="12">
@@ -2127,6 +2181,14 @@
         <f>Deals!C6</f>
         <v/>
       </c>
+      <c r="E12" s="159">
+        <f>Deals!D6</f>
+        <v/>
+      </c>
+      <c r="F12" s="159">
+        <f>Deals!E6</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2146,6 +2208,14 @@
         <f>Deals!C7</f>
         <v/>
       </c>
+      <c r="E13" s="159">
+        <f>Deals!D7</f>
+        <v/>
+      </c>
+      <c r="F13" s="159">
+        <f>Deals!E7</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2165,6 +2235,14 @@
         <f>Deals!C8</f>
         <v/>
       </c>
+      <c r="E14" s="139">
+        <f>Deals!D8</f>
+        <v/>
+      </c>
+      <c r="F14" s="139">
+        <f>Deals!E8</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2184,6 +2262,14 @@
         <f>Deals!C9</f>
         <v/>
       </c>
+      <c r="E15" s="139">
+        <f>Deals!D9</f>
+        <v/>
+      </c>
+      <c r="F15" s="139">
+        <f>Deals!E9</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2203,6 +2289,14 @@
         <f>Deals!C10</f>
         <v/>
       </c>
+      <c r="E16" s="139">
+        <f>Deals!D10</f>
+        <v/>
+      </c>
+      <c r="F16" s="139">
+        <f>Deals!E10</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -2222,6 +2316,14 @@
         <f>Deals!C11</f>
         <v/>
       </c>
+      <c r="E17" s="159">
+        <f>Deals!D11</f>
+        <v/>
+      </c>
+      <c r="F17" s="159">
+        <f>Deals!E11</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -2241,6 +2343,14 @@
         <f>Deals!C12</f>
         <v/>
       </c>
+      <c r="E18" s="139">
+        <f>Deals!D12</f>
+        <v/>
+      </c>
+      <c r="F18" s="139">
+        <f>Deals!E12</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -2260,6 +2370,14 @@
         <f>Deals!C13</f>
         <v/>
       </c>
+      <c r="E19" s="139">
+        <f>Deals!D13</f>
+        <v/>
+      </c>
+      <c r="F19" s="139">
+        <f>Deals!E13</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -2279,6 +2397,14 @@
         <f>Deals!C14</f>
         <v/>
       </c>
+      <c r="E20" s="139">
+        <f>Deals!D14</f>
+        <v/>
+      </c>
+      <c r="F20" s="139">
+        <f>Deals!E14</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -2298,6 +2424,14 @@
         <f>Deals!C15</f>
         <v/>
       </c>
+      <c r="E21" s="139">
+        <f>Deals!D15</f>
+        <v/>
+      </c>
+      <c r="F21" s="139">
+        <f>Deals!E15</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -2317,6 +2451,14 @@
         <f>Deals!C16</f>
         <v/>
       </c>
+      <c r="E22" s="139">
+        <f>Deals!D16</f>
+        <v/>
+      </c>
+      <c r="F22" s="139">
+        <f>Deals!E16</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -2336,6 +2478,14 @@
         <f>Deals!C17</f>
         <v/>
       </c>
+      <c r="E23" s="146">
+        <f>Deals!D17</f>
+        <v/>
+      </c>
+      <c r="F23" s="146">
+        <f>Deals!E17</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -2355,6 +2505,14 @@
         <f>Deals!C21</f>
         <v/>
       </c>
+      <c r="E24" s="146">
+        <f>Deals!D21</f>
+        <v/>
+      </c>
+      <c r="F24" s="146">
+        <f>Deals!E21</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -2374,6 +2532,14 @@
         <f>Deals!C22</f>
         <v/>
       </c>
+      <c r="E25" s="139">
+        <f>Deals!D22</f>
+        <v/>
+      </c>
+      <c r="F25" s="139">
+        <f>Deals!E22</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -2393,6 +2559,14 @@
         <f>Deals!C23</f>
         <v/>
       </c>
+      <c r="E26" s="139">
+        <f>Deals!D23</f>
+        <v/>
+      </c>
+      <c r="F26" s="139">
+        <f>Deals!E23</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -2412,6 +2586,14 @@
         <f>Deals!C24</f>
         <v/>
       </c>
+      <c r="E27" s="129">
+        <f>Deals!D24</f>
+        <v/>
+      </c>
+      <c r="F27" s="129">
+        <f>Deals!E24</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -2429,6 +2611,14 @@
       </c>
       <c r="D28" s="12">
         <f>Deals!C26</f>
+        <v/>
+      </c>
+      <c r="E28" s="139">
+        <f>Deals!D26</f>
+        <v/>
+      </c>
+      <c r="F28" s="139">
+        <f>Deals!E26</f>
         <v/>
       </c>
     </row>
@@ -2825,12 +3015,12 @@
           <t>Development</t>
         </is>
       </c>
-      <c r="D2" s="122" t="inlineStr">
+      <c r="D2" s="121" t="inlineStr">
         <is>
           <t>Development</t>
         </is>
       </c>
-      <c r="E2" s="123" t="inlineStr">
+      <c r="E2" s="160" t="inlineStr">
         <is>
           <t>Development</t>
         </is>
@@ -2875,12 +3065,12 @@
           <t>Hamburg</t>
         </is>
       </c>
-      <c r="D3" s="122" t="inlineStr">
+      <c r="D3" s="121" t="inlineStr">
         <is>
           <t>TX/OK/AR — workforce MF (placeholder mkt)</t>
         </is>
       </c>
-      <c r="E3" s="123" t="inlineStr">
+      <c r="E3" s="160" t="inlineStr">
         <is>
           <t>Modular factory — mfg business (placeholder mkt)</t>
         </is>
@@ -2905,10 +3095,10 @@
       <c r="C4" s="127" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="128" t="n">
+      <c r="D4" s="127" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="129" t="n">
+      <c r="E4" s="161" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="129">
@@ -2943,10 +3133,10 @@
       <c r="C5" s="131" t="n">
         <v>9592457</v>
       </c>
-      <c r="D5" s="132" t="n">
+      <c r="D5" s="131" t="n">
         <v>760660000</v>
       </c>
-      <c r="E5" s="133" t="n">
+      <c r="E5" s="162" t="n">
         <v>23500000</v>
       </c>
       <c r="F5" s="134" t="n"/>
@@ -2969,10 +3159,10 @@
       <c r="C6" s="131" t="n">
         <v>5773999</v>
       </c>
-      <c r="D6" s="132" t="n">
+      <c r="D6" s="131" t="n">
         <v>266231000</v>
       </c>
-      <c r="E6" s="133" t="n">
+      <c r="E6" s="162" t="n">
         <v>20000000</v>
       </c>
       <c r="F6" s="134" t="n"/>
@@ -2995,10 +3185,10 @@
       <c r="C7" s="131" t="n">
         <v>3818458</v>
       </c>
-      <c r="D7" s="132" t="n">
+      <c r="D7" s="131" t="n">
         <v>494429000</v>
       </c>
-      <c r="E7" s="133" t="n">
+      <c r="E7" s="162" t="n">
         <v>3500000</v>
       </c>
       <c r="F7" s="134" t="n"/>
@@ -3021,10 +3211,10 @@
       <c r="C8" s="137" t="n">
         <v>0.3980688159456957</v>
       </c>
-      <c r="D8" s="138" t="n">
+      <c r="D8" s="137" t="n">
         <v>0.65</v>
       </c>
-      <c r="E8" s="139" t="n">
+      <c r="E8" s="163" t="n">
         <v>0.148936170212766</v>
       </c>
       <c r="F8" s="139">
@@ -3057,8 +3247,8 @@
         <v>0.06999999924312052</v>
       </c>
       <c r="C9" s="137" t="n"/>
-      <c r="D9" s="138" t="n"/>
-      <c r="E9" s="139" t="n"/>
+      <c r="D9" s="137" t="n"/>
+      <c r="E9" s="163" t="n"/>
       <c r="F9" s="141" t="n"/>
       <c r="G9" s="142" t="n"/>
       <c r="H9" s="143" t="n"/>
@@ -3079,10 +3269,10 @@
       <c r="C10" s="137" t="n">
         <v>0.055</v>
       </c>
-      <c r="D10" s="138" t="n">
+      <c r="D10" s="137" t="n">
         <v>0.0602</v>
       </c>
-      <c r="E10" s="139" t="n">
+      <c r="E10" s="163" t="n">
         <v>0.1</v>
       </c>
       <c r="F10" s="141" t="n"/>
@@ -3105,10 +3295,10 @@
       <c r="C11" s="131" t="n">
         <v>706128.144158604</v>
       </c>
-      <c r="D11" s="132" t="n">
+      <c r="D11" s="131" t="n">
         <v>58728924</v>
       </c>
-      <c r="E11" s="133" t="n">
+      <c r="E11" s="162" t="n">
         <v>11984000</v>
       </c>
       <c r="F11" s="134" t="n"/>
@@ -3131,10 +3321,10 @@
       <c r="C12" s="137" t="n">
         <v>0.3529709367265373</v>
       </c>
-      <c r="D12" s="138" t="n">
+      <c r="D12" s="137" t="n">
         <v>0.224</v>
       </c>
-      <c r="E12" s="139" t="n">
+      <c r="E12" s="163" t="n">
         <v>0.7</v>
       </c>
       <c r="F12" s="141" t="n"/>
@@ -3157,10 +3347,10 @@
       <c r="C13" s="137" t="n">
         <v>0.07361285478356629</v>
       </c>
-      <c r="D13" s="138" t="n">
+      <c r="D13" s="137" t="n">
         <v>0.07720785107669656</v>
       </c>
-      <c r="E13" s="139" t="n">
+      <c r="E13" s="163" t="n">
         <v>0.5099574468085106</v>
       </c>
       <c r="F13" s="139">
@@ -3193,10 +3383,10 @@
       <c r="C14" s="137" t="n">
         <v>0.01861285478356629</v>
       </c>
-      <c r="D14" s="138" t="n">
+      <c r="D14" s="137" t="n">
         <v>0.01700785107669656</v>
       </c>
-      <c r="E14" s="139" t="n">
+      <c r="E14" s="163" t="n">
         <v>0.4099574468085107</v>
       </c>
       <c r="F14" s="139">
@@ -3231,8 +3421,8 @@
       <c r="C15" s="137" t="n">
         <v>0.1731</v>
       </c>
-      <c r="D15" s="138" t="n"/>
-      <c r="E15" s="139" t="n"/>
+      <c r="D15" s="137" t="n"/>
+      <c r="E15" s="163" t="n"/>
       <c r="F15" s="141" t="n"/>
       <c r="G15" s="142" t="n"/>
       <c r="H15" s="143" t="n"/>
@@ -3253,10 +3443,10 @@
       <c r="C16" s="137" t="n">
         <v>0.1691</v>
       </c>
-      <c r="D16" s="138" t="n">
+      <c r="D16" s="137" t="n">
         <v>0.129</v>
       </c>
-      <c r="E16" s="139" t="n">
+      <c r="E16" s="163" t="n">
         <v>0.282</v>
       </c>
       <c r="F16" s="141" t="n"/>
@@ -3277,8 +3467,8 @@
       <c r="C17" s="144" t="n">
         <v>63240</v>
       </c>
-      <c r="D17" s="145" t="n"/>
-      <c r="E17" s="146" t="n"/>
+      <c r="D17" s="144" t="n"/>
+      <c r="E17" s="164" t="n"/>
       <c r="F17" s="147" t="n"/>
       <c r="G17" s="148" t="n"/>
       <c r="H17" s="149" t="n"/>
@@ -3297,8 +3487,8 @@
       <c r="C18" s="144" t="n">
         <v>11.16</v>
       </c>
-      <c r="D18" s="145" t="n"/>
-      <c r="E18" s="146" t="n"/>
+      <c r="D18" s="144" t="n"/>
+      <c r="E18" s="164" t="n"/>
       <c r="F18" s="147" t="n"/>
       <c r="G18" s="148" t="n"/>
       <c r="H18" s="148" t="n"/>
@@ -3317,10 +3507,10 @@
       <c r="C19" s="144" t="n">
         <v>542</v>
       </c>
-      <c r="D19" s="145" t="n">
+      <c r="D19" s="144" t="n">
         <v>3300</v>
       </c>
-      <c r="E19" s="146" t="n">
+      <c r="E19" s="164" t="n">
         <v>700</v>
       </c>
       <c r="F19" s="147" t="n"/>
@@ -3341,8 +3531,8 @@
       <c r="C20" s="150" t="n">
         <v>16.74763438488299</v>
       </c>
-      <c r="D20" s="151" t="n"/>
-      <c r="E20" s="152" t="n"/>
+      <c r="D20" s="150" t="n"/>
+      <c r="E20" s="165" t="n"/>
       <c r="F20" s="153" t="n"/>
       <c r="G20" s="154" t="n"/>
       <c r="H20" s="154" t="n"/>
@@ -3363,10 +3553,10 @@
       <c r="C21" s="144" t="n">
         <v>250000</v>
       </c>
-      <c r="D21" s="145" t="n">
+      <c r="D21" s="144" t="n">
         <v>250000</v>
       </c>
-      <c r="E21" s="146" t="n">
+      <c r="E21" s="164" t="n">
         <v>250000</v>
       </c>
       <c r="F21" s="146">
@@ -3401,10 +3591,10 @@
       <c r="C22" s="137" t="n">
         <v>0.06</v>
       </c>
-      <c r="D22" s="138" t="n">
+      <c r="D22" s="137" t="n">
         <v>0.05</v>
       </c>
-      <c r="E22" s="139" t="n">
+      <c r="E22" s="163" t="n">
         <v>0.05</v>
       </c>
       <c r="F22" s="139">
@@ -3439,10 +3629,10 @@
       <c r="C23" s="137" t="n">
         <v>0.04</v>
       </c>
-      <c r="D23" s="138" t="n">
+      <c r="D23" s="137" t="n">
         <v>0.05</v>
       </c>
-      <c r="E23" s="139" t="n">
+      <c r="E23" s="163" t="n">
         <v>0.05</v>
       </c>
       <c r="F23" s="139">
@@ -3473,8 +3663,8 @@
       </c>
       <c r="B24" s="127" t="n"/>
       <c r="C24" s="127" t="n"/>
-      <c r="D24" s="128" t="n"/>
-      <c r="E24" s="129" t="n"/>
+      <c r="D24" s="127" t="n"/>
+      <c r="E24" s="161" t="n"/>
       <c r="F24" s="129">
         <f>IFERROR(VLOOKUP(F3,MarketTable,5,FALSE),"")</f>
         <v/>
@@ -3503,8 +3693,8 @@
       </c>
       <c r="B25" s="150" t="n"/>
       <c r="C25" s="150" t="n"/>
-      <c r="D25" s="151" t="n"/>
-      <c r="E25" s="152" t="n"/>
+      <c r="D25" s="150" t="n"/>
+      <c r="E25" s="165" t="n"/>
       <c r="F25" s="152">
         <f>IFERROR(VLOOKUP(F3,MarketTable,6,FALSE),"")</f>
         <v/>
@@ -3539,11 +3729,11 @@
         <f>IF(COUNT(C15:C16)=0,"",MAX(C15:C16))</f>
         <v/>
       </c>
-      <c r="D26" s="138">
+      <c r="D26" s="137">
         <f>IF(COUNT(D15:D16)=0,"",MAX(D15:D16))</f>
         <v/>
       </c>
-      <c r="E26" s="139">
+      <c r="E26" s="163">
         <f>IF(COUNT(E15:E16)=0,"",MAX(E15:E16))</f>
         <v/>
       </c>
@@ -3581,11 +3771,11 @@
         <f>IF(C4=1,C13,C9)</f>
         <v/>
       </c>
-      <c r="D27" s="138">
+      <c r="D27" s="137">
         <f>IF(D4=1,D13,D9)</f>
         <v/>
       </c>
-      <c r="E27" s="139">
+      <c r="E27" s="163">
         <f>IF(E4=1,E13,E9)</f>
         <v/>
       </c>
@@ -4083,7 +4273,6 @@
       <c r="K10" s="10" t="n"/>
       <c r="L10" s="10" t="n"/>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>

--- a/ICGoNoGoDashboard_Working.xlsx
+++ b/ICGoNoGoDashboard_Working.xlsx
@@ -2598,7 +2598,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Best IRR (calc)</t>
+          <t>Equity IRR (calc, levered)</t>
         </is>
       </c>
       <c r="B28" s="12">
@@ -3718,44 +3718,53 @@
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
         <is>
-          <t>Best IRR (calc)</t>
+          <t>Equity IRR (calc, levered)</t>
         </is>
       </c>
       <c r="B26" s="138">
-        <f>IF(COUNT(B15:B16)=0,"",MAX(B15:B16))</f>
+        <f>IF(ISNUMBER(B16),B16,IF(ISNUMBER(B15),B15,""))</f>
         <v/>
       </c>
       <c r="C26" s="138">
-        <f>IF(COUNT(C15:C16)=0,"",MAX(C15:C16))</f>
+        <f>IF(ISNUMBER(C16),C16,IF(ISNUMBER(C15),C15,""))</f>
         <v/>
       </c>
       <c r="D26" s="137">
-        <f>IF(COUNT(D15:D16)=0,"",MAX(D15:D16))</f>
+        <f>IF(ISNUMBER(D16),D16,IF(ISNUMBER(D15),D15,""))</f>
         <v/>
       </c>
       <c r="E26" s="163">
-        <f>IF(COUNT(E15:E16)=0,"",MAX(E15:E16))</f>
+        <f>IF(ISNUMBER(E16),E16,IF(ISNUMBER(E15),E15,""))</f>
         <v/>
       </c>
       <c r="F26" s="139">
-        <f>IF(COUNT(F15:F16)=0,"",MAX(F15:F16))</f>
+        <f>IF(ISNUMBER(F16),F16,IF(ISNUMBER(F15),F15,""))</f>
         <v/>
       </c>
       <c r="G26" s="140">
-        <f>IF(COUNT(G15:G16)=0,"",MAX(G15:G16))</f>
+        <f>IF(ISNUMBER(G16),G16,IF(ISNUMBER(G15),G15,""))</f>
         <v/>
       </c>
       <c r="H26" s="140">
-        <f>IF(COUNT(H15:H16)=0,"",MAX(H15:H16))</f>
+        <f>IF(ISNUMBER(H16),H16,IF(ISNUMBER(H15),H15,""))</f>
         <v/>
       </c>
       <c r="I26" s="140">
-        <f>IF(COUNT(I15:I16)=0,"",MAX(I15:I16))</f>
-        <v/>
-      </c>
-      <c r="J26" s="42" t="n"/>
-      <c r="K26" s="42" t="n"/>
-      <c r="L26" s="42" t="n"/>
+        <f>IF(ISNUMBER(I16),I16,IF(ISNUMBER(I15),I15,""))</f>
+        <v/>
+      </c>
+      <c r="J26" s="42">
+        <f>IF(ISNUMBER(J16),J16,IF(ISNUMBER(J15),J15,""))</f>
+        <v/>
+      </c>
+      <c r="K26" s="42">
+        <f>IF(ISNUMBER(K16),K16,IF(ISNUMBER(K15),K15,""))</f>
+        <v/>
+      </c>
+      <c r="L26" s="42">
+        <f>IF(ISNUMBER(L16),L16,IF(ISNUMBER(L15),L15,""))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="21" t="inlineStr">

--- a/ICGoNoGoDashboard_Working.xlsx
+++ b/ICGoNoGoDashboard_Working.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Ranking" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Market Ranking" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Market Data" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="Cash Flows" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="MarketCounties">'Market Data'!$A$2:$A$247</definedName>
@@ -35,7 +36,7 @@
     <numFmt numFmtId="170" formatCode="0_);\(0\)"/>
     <numFmt numFmtId="171" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -168,8 +169,11 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -246,6 +250,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -529,7 +538,7 @@
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -937,6 +946,23 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="14" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="13" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2939,7 +2965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22.1796875" bestFit="1" customWidth="1" style="54" min="1" max="1"/>
@@ -3718,39 +3744,39 @@
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
         <is>
-          <t>Equity IRR (calc, levered)</t>
+          <t>Equity IRR (used)</t>
         </is>
       </c>
       <c r="B26" s="138">
-        <f>IF(ISNUMBER(B16),B16,IF(ISNUMBER(B15),B15,""))</f>
+        <f>IF(ISNUMBER(B28),B28,IF(ISNUMBER(B16),B16,IF(ISNUMBER(B15),B15,"")))</f>
         <v/>
       </c>
       <c r="C26" s="138">
-        <f>IF(ISNUMBER(C16),C16,IF(ISNUMBER(C15),C15,""))</f>
+        <f>IF(ISNUMBER(C28),C28,IF(ISNUMBER(C16),C16,IF(ISNUMBER(C15),C15,"")))</f>
         <v/>
       </c>
       <c r="D26" s="137">
-        <f>IF(ISNUMBER(D16),D16,IF(ISNUMBER(D15),D15,""))</f>
+        <f>IF(ISNUMBER(D28),D28,IF(ISNUMBER(D16),D16,IF(ISNUMBER(D15),D15,"")))</f>
         <v/>
       </c>
       <c r="E26" s="163">
-        <f>IF(ISNUMBER(E16),E16,IF(ISNUMBER(E15),E15,""))</f>
+        <f>IF(ISNUMBER(E28),E28,IF(ISNUMBER(E16),E16,IF(ISNUMBER(E15),E15,"")))</f>
         <v/>
       </c>
       <c r="F26" s="139">
-        <f>IF(ISNUMBER(F16),F16,IF(ISNUMBER(F15),F15,""))</f>
+        <f>IF(ISNUMBER(F28),F28,IF(ISNUMBER(F16),F16,IF(ISNUMBER(F15),F15,"")))</f>
         <v/>
       </c>
       <c r="G26" s="140">
-        <f>IF(ISNUMBER(G16),G16,IF(ISNUMBER(G15),G15,""))</f>
+        <f>IF(ISNUMBER(G28),G28,IF(ISNUMBER(G16),G16,IF(ISNUMBER(G15),G15,"")))</f>
         <v/>
       </c>
       <c r="H26" s="140">
-        <f>IF(ISNUMBER(H16),H16,IF(ISNUMBER(H15),H15,""))</f>
+        <f>IF(ISNUMBER(H28),H28,IF(ISNUMBER(H16),H16,IF(ISNUMBER(H15),H15,"")))</f>
         <v/>
       </c>
       <c r="I26" s="140">
-        <f>IF(ISNUMBER(I16),I16,IF(ISNUMBER(I15),I15,""))</f>
+        <f>IF(ISNUMBER(I28),I28,IF(ISNUMBER(I16),I16,IF(ISNUMBER(I15),I15,"")))</f>
         <v/>
       </c>
       <c r="J26" s="42">
@@ -3807,6 +3833,45 @@
       <c r="J27" s="42" t="n"/>
       <c r="K27" s="42" t="n"/>
       <c r="L27" s="42" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="166" t="inlineStr">
+        <is>
+          <t>Calculated IRR (=IRR)</t>
+        </is>
+      </c>
+      <c r="B28" s="167">
+        <f>IFERROR('Cash Flows'!B15,"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="167">
+        <f>IFERROR('Cash Flows'!C15,"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="167">
+        <f>IFERROR('Cash Flows'!D15,"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="167">
+        <f>IFERROR('Cash Flows'!E15,"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="167">
+        <f>IFERROR('Cash Flows'!F15,"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="167">
+        <f>IFERROR('Cash Flows'!G15,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="167">
+        <f>IFERROR('Cash Flows'!H15,"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="167">
+        <f>IFERROR('Cash Flows'!I15,"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="8">
@@ -29751,4 +29816,370 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="54" min="1" max="1"/>
+    <col width="16" customWidth="1" style="54" min="2" max="2"/>
+    <col width="16" customWidth="1" style="54" min="3" max="3"/>
+    <col width="16" customWidth="1" style="54" min="4" max="4"/>
+    <col width="16" customWidth="1" style="54" min="5" max="5"/>
+    <col width="16" customWidth="1" style="54" min="6" max="6"/>
+    <col width="16" customWidth="1" style="54" min="7" max="7"/>
+    <col width="16" customWidth="1" style="54" min="8" max="8"/>
+    <col width="16" customWidth="1" style="54" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="168" t="inlineStr">
+        <is>
+          <t>Annual EQUITY cash flow — Year 0 = −equity invested.  Edit any cell with the deal's actual figures; =IRR recomputes below.  Reference streams are seeded so =IRR reproduces each model's stated IRR — replace with real cash flows for a fully bottom-up IRR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="169" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B2" s="170">
+        <f>Deals!B1</f>
+        <v/>
+      </c>
+      <c r="C2" s="170">
+        <f>Deals!C1</f>
+        <v/>
+      </c>
+      <c r="D2" s="170">
+        <f>Deals!D1</f>
+        <v/>
+      </c>
+      <c r="E2" s="170">
+        <f>Deals!E1</f>
+        <v/>
+      </c>
+      <c r="F2" s="170">
+        <f>Deals!F1</f>
+        <v/>
+      </c>
+      <c r="G2" s="170">
+        <f>Deals!G1</f>
+        <v/>
+      </c>
+      <c r="H2" s="170">
+        <f>Deals!H1</f>
+        <v/>
+      </c>
+      <c r="I2" s="170">
+        <f>Deals!I1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="166" t="inlineStr">
+        <is>
+          <t>Year 0</t>
+        </is>
+      </c>
+      <c r="B3" s="171" t="n">
+        <v>-13212143</v>
+      </c>
+      <c r="C3" s="171" t="n">
+        <v>-5773999</v>
+      </c>
+      <c r="D3" s="171" t="n">
+        <v>-266231000</v>
+      </c>
+      <c r="E3" s="171" t="n">
+        <v>-20000000</v>
+      </c>
+      <c r="F3" s="172" t="n"/>
+      <c r="G3" s="172" t="n"/>
+      <c r="H3" s="172" t="n"/>
+      <c r="I3" s="172" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="166" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
+      </c>
+      <c r="B4" s="171" t="n">
+        <v>924850</v>
+      </c>
+      <c r="C4" s="171" t="n">
+        <v>438836.08</v>
+      </c>
+      <c r="D4" s="171" t="n">
+        <v>24118894</v>
+      </c>
+      <c r="E4" s="171" t="n">
+        <v>11739000</v>
+      </c>
+      <c r="F4" s="172" t="n"/>
+      <c r="G4" s="172" t="n"/>
+      <c r="H4" s="172" t="n"/>
+      <c r="I4" s="172" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="166" t="inlineStr">
+        <is>
+          <t>Year 2</t>
+        </is>
+      </c>
+      <c r="B5" s="171" t="n">
+        <v>924850</v>
+      </c>
+      <c r="C5" s="171" t="n">
+        <v>438836.08</v>
+      </c>
+      <c r="D5" s="171" t="n">
+        <v>24118894</v>
+      </c>
+      <c r="E5" s="171" t="n">
+        <v>11739000</v>
+      </c>
+      <c r="F5" s="172" t="n"/>
+      <c r="G5" s="172" t="n"/>
+      <c r="H5" s="172" t="n"/>
+      <c r="I5" s="172" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="166" t="inlineStr">
+        <is>
+          <t>Year 3</t>
+        </is>
+      </c>
+      <c r="B6" s="171" t="n">
+        <v>924850</v>
+      </c>
+      <c r="C6" s="171" t="n">
+        <v>438836.08</v>
+      </c>
+      <c r="D6" s="171" t="n">
+        <v>24118894</v>
+      </c>
+      <c r="E6" s="171" t="n">
+        <v>11739000</v>
+      </c>
+      <c r="F6" s="172" t="n"/>
+      <c r="G6" s="172" t="n"/>
+      <c r="H6" s="172" t="n"/>
+      <c r="I6" s="172" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="166" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B7" s="171" t="n">
+        <v>924850</v>
+      </c>
+      <c r="C7" s="171" t="n">
+        <v>438836.08</v>
+      </c>
+      <c r="D7" s="171" t="n">
+        <v>24118894</v>
+      </c>
+      <c r="E7" s="171" t="n">
+        <v>11739000</v>
+      </c>
+      <c r="F7" s="172" t="n"/>
+      <c r="G7" s="172" t="n"/>
+      <c r="H7" s="172" t="n"/>
+      <c r="I7" s="172" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="166" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B8" s="171" t="n">
+        <v>924850</v>
+      </c>
+      <c r="C8" s="171" t="n">
+        <v>9976709.42</v>
+      </c>
+      <c r="D8" s="171" t="n">
+        <v>356478652.86</v>
+      </c>
+      <c r="E8" s="171" t="n">
+        <v>11739000</v>
+      </c>
+      <c r="F8" s="172" t="n"/>
+      <c r="G8" s="172" t="n"/>
+      <c r="H8" s="172" t="n"/>
+      <c r="I8" s="172" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="166" t="inlineStr">
+        <is>
+          <t>Year 6</t>
+        </is>
+      </c>
+      <c r="B9" s="171" t="n">
+        <v>924850</v>
+      </c>
+      <c r="C9" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="171" t="n">
+        <v>11739000</v>
+      </c>
+      <c r="F9" s="172" t="n"/>
+      <c r="G9" s="172" t="n"/>
+      <c r="H9" s="172" t="n"/>
+      <c r="I9" s="172" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="166" t="inlineStr">
+        <is>
+          <t>Year 7</t>
+        </is>
+      </c>
+      <c r="B10" s="171" t="n">
+        <v>19753090.13</v>
+      </c>
+      <c r="C10" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="171" t="n">
+        <v>11739000</v>
+      </c>
+      <c r="F10" s="172" t="n"/>
+      <c r="G10" s="172" t="n"/>
+      <c r="H10" s="172" t="n"/>
+      <c r="I10" s="172" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="166" t="inlineStr">
+        <is>
+          <t>Year 8</t>
+        </is>
+      </c>
+      <c r="B11" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="171" t="n">
+        <v>11739000</v>
+      </c>
+      <c r="F11" s="172" t="n"/>
+      <c r="G11" s="172" t="n"/>
+      <c r="H11" s="172" t="n"/>
+      <c r="I11" s="172" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="166" t="inlineStr">
+        <is>
+          <t>Year 9</t>
+        </is>
+      </c>
+      <c r="B12" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="171" t="n">
+        <v>11739000</v>
+      </c>
+      <c r="F12" s="172" t="n"/>
+      <c r="G12" s="172" t="n"/>
+      <c r="H12" s="172" t="n"/>
+      <c r="I12" s="172" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="166" t="inlineStr">
+        <is>
+          <t>Year 10</t>
+        </is>
+      </c>
+      <c r="B13" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="171" t="n">
+        <v>-205985445.2</v>
+      </c>
+      <c r="F13" s="172" t="n"/>
+      <c r="G13" s="172" t="n"/>
+      <c r="H13" s="172" t="n"/>
+      <c r="I13" s="172" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="166" t="inlineStr">
+        <is>
+          <t>Calculated IRR (=IRR)</t>
+        </is>
+      </c>
+      <c r="B15" s="174">
+        <f>IFERROR(IRR(B3:B13),"")</f>
+        <v/>
+      </c>
+      <c r="C15" s="174">
+        <f>IFERROR(IRR(C3:C13),"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="174">
+        <f>IFERROR(IRR(D3:D13),"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="174">
+        <f>IFERROR(IRR(E3:E13),"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="174">
+        <f>IFERROR(IRR(F3:F13),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="174">
+        <f>IFERROR(IRR(G3:G13),"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="174">
+        <f>IFERROR(IRR(H3:H13),"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="174">
+        <f>IFERROR(IRR(I3:I13),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/ICGoNoGoDashboard_Working.xlsx
+++ b/ICGoNoGoDashboard_Working.xlsx
@@ -2038,11 +2038,7 @@
           <t>Closest archetype</t>
         </is>
       </c>
-      <c r="E5" s="55" t="inlineStr">
-        <is>
-          <t>Import File Button</t>
-        </is>
-      </c>
+      <c r="E5" s="55" t="n"/>
       <c r="J5" s="2">
         <f>Deals!F1</f>
         <v/>
